--- a/12600717.xlsx
+++ b/12600717.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python Minor Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A4669D8-1424-449B-AC45-5521E899E36A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24884B55-9BC4-4D2C-AB15-7F2623D5A770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -202,157 +202,136 @@
     <t>High</t>
   </si>
   <si>
-    <t>Productive</t>
-  </si>
-  <si>
-    <t>Tired</t>
-  </si>
-  <si>
     <t>Neutral</t>
   </si>
   <si>
     <t>Low</t>
   </si>
   <si>
-    <t>Energetic</t>
-  </si>
-  <si>
-    <t>Exhausted</t>
-  </si>
-  <si>
-    <t>Refreshed</t>
-  </si>
-  <si>
-    <t>Attended 5 classes; maintained focus and completed evening study session.</t>
-  </si>
-  <si>
-    <t>Attended 5 classes; successfully covered lab work and assignment tasks.</t>
-  </si>
-  <si>
-    <t>Lighter schedule with 4 classes; steady energy for personal study.</t>
-  </si>
-  <si>
-    <t>Packed schedule with 6 classes; felt drained by late afternoon.</t>
-  </si>
-  <si>
-    <t>Heavy 7-class schedule; managed to complete all lectures but needed rest in evening.</t>
-  </si>
-  <si>
-    <t>No classes; dedicated day to recovery, project coding, and leisure.</t>
-  </si>
-  <si>
-    <t>Relaxed</t>
-  </si>
-  <si>
-    <t>Highly Satisfied</t>
-  </si>
-  <si>
-    <t>Sunday break; reviewed weak concepts and prepared schedule for upcoming week.</t>
-  </si>
-  <si>
-    <t>Attended 5 classes; started week with solid momentum and evening coding session.</t>
-  </si>
-  <si>
-    <t>Attended 5 classes; stayed on track with coursework and made solid progress on programming tasks.</t>
-  </si>
-  <si>
-    <t>Busy day with 6 classes; stayed attentive and finished daily lab work.</t>
-  </si>
-  <si>
-    <t>Heavy 7-class schedule; completed classes and spent time on coding project.</t>
-  </si>
-  <si>
-    <t>Weekend study routine; made major progress on project implementation.</t>
-  </si>
-  <si>
-    <t>Rest and reset day; caught up on reading and prepared for the week ahead.</t>
-  </si>
-  <si>
-    <t>Attended 5 classes; smooth start to the week with steady study hours.</t>
-  </si>
-  <si>
-    <t>Attended 5 classes; completed practice problems and coding tasks.</t>
-  </si>
-  <si>
-    <t>Balanced day with 4 classes; focused on workout and core subject review.</t>
-  </si>
-  <si>
-    <t>Attended 6 classes; managed homework assignments in the evening.</t>
-  </si>
-  <si>
-    <t>End of the week with 7 classes; wrapped up pending lab write-ups.</t>
-  </si>
-  <si>
-    <t>Lighter lecture schedule completed study goals and evening revision.</t>
-  </si>
-  <si>
-    <t>Saturday self-study session; devoted significant time to full-stack project building.</t>
-  </si>
-  <si>
-    <t>Sunday rest day; organized study materials and reviewed core concepts.</t>
-  </si>
-  <si>
-    <t>Attended 5 classes; started the week focused with an evening problem-solving session.</t>
-  </si>
-  <si>
-    <t>Attended 5 classes; completed lab work efficiently and made progress on code repo.</t>
-  </si>
-  <si>
-    <t>Lighter 4-class day; balanced fitness workout with evening assignment work.</t>
-  </si>
-  <si>
-    <t>Busy day with 6 classes; stayed focused in lectures and revised evening notes.</t>
-  </si>
-  <si>
-    <t>End of the week with 7 classes; completed weekly deliverables and lab write-ups.</t>
-  </si>
-  <si>
-    <t>Attended 6 classes; completed reading assignments in evening.</t>
-  </si>
-  <si>
-    <t>End of busy week with 7 classes; finished pending lab reports.</t>
-  </si>
-  <si>
-    <t>Independence Day break; devoted time to coding project and study.</t>
-  </si>
-  <si>
-    <t>Sunday leisure and preparation for week ahead.</t>
-  </si>
-  <si>
-    <t>Attended 5 classes; active participation in discussions.</t>
-  </si>
-  <si>
-    <t>Attended 5 classes; worked on programming exercise tasks.</t>
-  </si>
-  <si>
-    <t>Lighter 4-class day; balanced study with fitness workout.</t>
-  </si>
-  <si>
-    <t>Attended 6 classes; reviewed core subject notes.</t>
-  </si>
-  <si>
-    <t>End of academic week with 7 classes; completed weekly logs.</t>
-  </si>
-  <si>
-    <t>Weekend study routine; focused on algorithm problem solving.</t>
-  </si>
-  <si>
-    <t>Sunday break; organized week plan and relaxed.</t>
-  </si>
-  <si>
     <t>SHANTANU CHHETRI</t>
   </si>
   <si>
-    <t>AUGUST | SEPTEMBER</t>
+    <t>Excellent</t>
   </si>
   <si>
-    <t>Saturday coding deep dive; completed full-stack microservice integration and API endpoints.</t>
+    <t>Very Satisfied</t>
   </si>
   <si>
-    <t>Sunday rest day; catch-up reading, weekly schedule review, and project planning.</t>
+    <t>Stressed</t>
   </si>
   <si>
-    <t>Attended 5 classes; productive week start with evening competitive programming practice.</t>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Revised DBMS and practiced SQL.</t>
+  </si>
+  <si>
+    <t>Focused on algorithm problem solving.</t>
+  </si>
+  <si>
+    <t>Sunday rest and DSA revision.</t>
+  </si>
+  <si>
+    <t>Attended classes and study session.</t>
+  </si>
+  <si>
+    <t>Covered lab work and assignment tasks.</t>
+  </si>
+  <si>
+    <t>Relaxed Sunday and light revision.</t>
+  </si>
+  <si>
+    <t>Started week with solid momentum and evening coding session.</t>
+  </si>
+  <si>
+    <t>Stayed on track with coursework.</t>
+  </si>
+  <si>
+    <t>Completed study goals and evening revision.</t>
+  </si>
+  <si>
+    <t>Stayed attentive and finished daily lab work.</t>
+  </si>
+  <si>
+    <t>Practiced SQL joins and subqueries.</t>
+  </si>
+  <si>
+    <t>Outing with friends and rest.</t>
+  </si>
+  <si>
+    <t>Smooth start to the week with steady study hours.</t>
+  </si>
+  <si>
+    <t>Completed practice problems and coding tasks.</t>
+  </si>
+  <si>
+    <t>Focused on workout and core subject review.</t>
+  </si>
+  <si>
+    <t>Managed homework assignments in the evening.</t>
+  </si>
+  <si>
+    <t>Wrapped up pending lab write-ups.</t>
+  </si>
+  <si>
+    <t>Took CA quiz and prepared viva.</t>
+  </si>
+  <si>
+    <t>Practiced dynamic programming in evening.</t>
+  </si>
+  <si>
+    <t>Completed lab work efficiently.</t>
+  </si>
+  <si>
+    <t>Balanced fitness workout with evening assignment work.</t>
+  </si>
+  <si>
+    <t>Slight headache after six classes.</t>
+  </si>
+  <si>
+    <t>Revised C++ Pointers.</t>
+  </si>
+  <si>
+    <t>Practiced Networking Practical Task.</t>
+  </si>
+  <si>
+    <t>Productive week start with evening programming practice.</t>
+  </si>
+  <si>
+    <t>Solved problems on LeetCode.</t>
+  </si>
+  <si>
+    <t>Reviewed LinkedIn Profile.</t>
+  </si>
+  <si>
+    <t>Tired day, finished C++ Practical Assignment Question.</t>
+  </si>
+  <si>
+    <t>Solved Problems on Leetcode.</t>
+  </si>
+  <si>
+    <t>Revised DBMS Normalizations.</t>
+  </si>
+  <si>
+    <t>Solved Leetcode problems on Saturday.</t>
+  </si>
+  <si>
+    <t>Learned new concepts of OOPS in Python.</t>
+  </si>
+  <si>
+    <t>Devoted significant time to Logic Building.</t>
+  </si>
+  <si>
+    <t>AUGUST, SEPTEMBER</t>
+  </si>
+  <si>
+    <t>Completed Unit 2 in Analytical Subject.</t>
+  </si>
+  <si>
+    <t>Exhausting Friday, took rest.</t>
+  </si>
+  <si>
+    <t>Completed C++ Fundamental Concepts.</t>
   </si>
 </sst>
 </file>
@@ -1010,7 +989,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N412"/>
+  <dimension ref="A1:N408"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1047,7 +1026,7 @@
         <v>30</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
@@ -1072,7 +1051,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="G3" s="20"/>
     </row>
@@ -1138,314 +1117,314 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B6" s="9">
+        <v>420</v>
+      </c>
+      <c r="C6" s="9">
+        <v>40</v>
+      </c>
+      <c r="D6" s="9">
+        <v>110</v>
+      </c>
+      <c r="E6" s="9">
+        <v>85</v>
+      </c>
+      <c r="F6" s="9">
+        <v>250</v>
+      </c>
+      <c r="G6" s="9">
+        <v>5</v>
+      </c>
+      <c r="H6" s="9">
+        <v>165</v>
+      </c>
+      <c r="I6" s="14">
+        <f t="shared" ref="I6:I10" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <v>1070</v>
+      </c>
+      <c r="J6" s="14">
+        <f t="shared" ref="J6:J13" si="1">IF(I6="","",1440-I6)</f>
+        <v>370</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="L6" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="M6" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
+        <v>46252</v>
+      </c>
+      <c r="B7" s="9">
         <v>450</v>
       </c>
-      <c r="C6" s="9">
-        <v>30</v>
-      </c>
-      <c r="D6" s="9">
-        <v>120</v>
-      </c>
-      <c r="E6" s="9">
-        <v>90</v>
-      </c>
-      <c r="F6" s="9">
-        <v>300</v>
-      </c>
-      <c r="G6" s="9">
-        <v>6</v>
-      </c>
-      <c r="H6" s="9">
-        <v>180</v>
-      </c>
-      <c r="I6" s="14">
-        <f t="shared" ref="I6:I14" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
-        <v>1170</v>
-      </c>
-      <c r="J6" s="14">
-        <f t="shared" ref="J6:J17" si="1">IF(I6="","",1440-I6)</f>
-        <v>270</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="M6" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="N6" s="11" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
-        <v>46248</v>
-      </c>
-      <c r="B7" s="9">
-        <v>420</v>
-      </c>
       <c r="C7" s="9">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D7" s="9">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="E7" s="9">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="F7" s="9">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="G7" s="9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H7" s="9">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="I7" s="14">
         <f t="shared" si="0"/>
-        <v>1190</v>
+        <v>1115</v>
       </c>
       <c r="J7" s="14">
         <f t="shared" si="1"/>
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="L7" s="10" t="s">
         <v>50</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
-        <v>46249</v>
+        <v>46253</v>
       </c>
       <c r="B8" s="9">
-        <v>510</v>
+        <v>420</v>
       </c>
       <c r="C8" s="9">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D8" s="9">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="E8" s="9">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="F8" s="9">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G8" s="9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H8" s="9">
-        <v>240</v>
+        <v>195</v>
       </c>
       <c r="I8" s="14">
         <f t="shared" si="0"/>
-        <v>1140</v>
+        <v>1080</v>
       </c>
       <c r="J8" s="14">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="M8" s="10" t="s">
         <v>54</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
-        <v>46250</v>
+        <v>46254</v>
       </c>
       <c r="B9" s="9">
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="C9" s="9">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D9" s="9">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="E9" s="9">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="F9" s="9">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G9" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H9" s="9">
-        <v>300</v>
+        <v>160</v>
       </c>
       <c r="I9" s="14">
         <f t="shared" si="0"/>
-        <v>1095</v>
+        <v>1125</v>
       </c>
       <c r="J9" s="14">
         <f t="shared" si="1"/>
-        <v>345</v>
+        <v>315</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
-        <v>46251</v>
+        <v>46255</v>
       </c>
       <c r="B10" s="9">
         <v>420</v>
       </c>
       <c r="C10" s="9">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D10" s="9">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="E10" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F10" s="9">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="G10" s="9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H10" s="9">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="I10" s="14">
         <f t="shared" si="0"/>
-        <v>1105</v>
+        <v>1115</v>
       </c>
       <c r="J10" s="14">
         <f t="shared" si="1"/>
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
-        <v>46252</v>
+        <v>46256</v>
       </c>
       <c r="B11" s="9">
-        <v>450</v>
+        <v>510</v>
       </c>
       <c r="C11" s="9">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="D11" s="9">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E11" s="9">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="F11" s="9">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G11" s="9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H11" s="9">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="I11" s="14">
-        <f t="shared" si="0"/>
-        <v>1150</v>
+        <f t="shared" ref="I11:I76" si="2">IF(SUM(B11:F11,H11)=0,"",SUM(B11:F11,H11))</f>
+        <v>1110</v>
       </c>
       <c r="J11" s="14">
         <f t="shared" si="1"/>
-        <v>290</v>
+        <v>330</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="M11" s="10" t="s">
         <v>54</v>
       </c>
       <c r="N11" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="8">
+        <v>46257</v>
+      </c>
+      <c r="B12" s="9">
+        <v>480</v>
+      </c>
+      <c r="C12" s="9">
+        <v>40</v>
+      </c>
+      <c r="D12" s="9">
+        <v>125</v>
+      </c>
+      <c r="E12" s="9">
         <v>95</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
-        <v>46253</v>
-      </c>
-      <c r="B12" s="9">
-        <v>420</v>
-      </c>
-      <c r="C12" s="9">
-        <v>60</v>
-      </c>
-      <c r="D12" s="9">
-        <v>120</v>
-      </c>
-      <c r="E12" s="9">
-        <v>90</v>
-      </c>
       <c r="F12" s="9">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G12" s="9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H12" s="9">
-        <v>180</v>
+        <v>285</v>
       </c>
       <c r="I12" s="14">
-        <f t="shared" si="0"/>
-        <v>1070</v>
+        <f t="shared" si="2"/>
+        <v>1025</v>
       </c>
       <c r="J12" s="14">
         <f t="shared" si="1"/>
-        <v>370</v>
+        <v>415</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>49</v>
@@ -1454,320 +1433,320 @@
         <v>50</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B13" s="9">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="C13" s="9">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D13" s="9">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="E13" s="9">
         <v>90</v>
       </c>
       <c r="F13" s="9">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G13" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H13" s="9">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="I13" s="14">
-        <f t="shared" si="0"/>
-        <v>1170</v>
+        <f t="shared" si="2"/>
+        <v>1085</v>
       </c>
       <c r="J13" s="14">
         <f t="shared" si="1"/>
-        <v>270</v>
+        <v>355</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B14" s="9">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="C14" s="9">
         <v>30</v>
       </c>
       <c r="D14" s="9">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="E14" s="9">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="F14" s="9">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="G14" s="9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H14" s="9">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="0"/>
-        <v>1190</v>
+        <f t="shared" si="2"/>
+        <v>1135</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="1"/>
-        <v>250</v>
+        <f t="shared" ref="J14:J76" si="3">IF(I14="","",1440-I14)</f>
+        <v>305</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="L14" s="10" t="s">
         <v>50</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
-        <v>46256</v>
+        <v>46260</v>
       </c>
       <c r="B15" s="9">
-        <v>510</v>
+        <v>420</v>
       </c>
       <c r="C15" s="9">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D15" s="9">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="E15" s="9">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="F15" s="9">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G15" s="9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H15" s="9">
-        <v>240</v>
+        <v>185</v>
       </c>
       <c r="I15" s="14">
-        <f t="shared" ref="I15:I80" si="2">IF(SUM(B15:F15,H15)=0,"",SUM(B15:F15,H15))</f>
-        <v>1140</v>
+        <f t="shared" si="2"/>
+        <v>1080</v>
       </c>
       <c r="J15" s="14">
-        <f t="shared" si="1"/>
-        <v>300</v>
+        <f t="shared" si="3"/>
+        <v>360</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="M15" s="10" t="s">
         <v>54</v>
       </c>
       <c r="N15" s="11" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="B16" s="9">
         <v>480</v>
       </c>
       <c r="C16" s="9">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D16" s="9">
+        <v>130</v>
+      </c>
+      <c r="E16" s="9">
+        <v>65</v>
+      </c>
+      <c r="F16" s="9">
+        <v>300</v>
+      </c>
+      <c r="G16" s="9">
+        <v>6</v>
+      </c>
+      <c r="H16" s="9">
         <v>150</v>
-      </c>
-      <c r="E16" s="9">
-        <v>120</v>
-      </c>
-      <c r="F16" s="9">
-        <v>0</v>
-      </c>
-      <c r="G16" s="9">
-        <v>0</v>
-      </c>
-      <c r="H16" s="9">
-        <v>300</v>
       </c>
       <c r="I16" s="14">
         <f t="shared" si="2"/>
-        <v>1095</v>
+        <v>1150</v>
       </c>
       <c r="J16" s="14">
-        <f t="shared" si="1"/>
-        <v>345</v>
+        <f t="shared" si="3"/>
+        <v>290</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="N16" s="11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="B17" s="9">
         <v>420</v>
       </c>
       <c r="C17" s="9">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="D17" s="9">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="E17" s="9">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F17" s="9">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="G17" s="9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H17" s="9">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="I17" s="14">
         <f t="shared" si="2"/>
-        <v>1105</v>
+        <v>1115</v>
       </c>
       <c r="J17" s="14">
-        <f t="shared" si="1"/>
-        <v>335</v>
+        <f t="shared" si="3"/>
+        <v>325</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
-        <v>46259</v>
+        <v>46263</v>
       </c>
       <c r="B18" s="9">
-        <v>450</v>
+        <v>510</v>
       </c>
       <c r="C18" s="9">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D18" s="9">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E18" s="9">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="F18" s="9">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G18" s="9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H18" s="9">
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="I18" s="14">
         <f t="shared" si="2"/>
-        <v>1150</v>
+        <v>1130</v>
       </c>
       <c r="J18" s="14">
-        <f t="shared" ref="J18:J80" si="3">IF(I18="","",1440-I18)</f>
-        <v>290</v>
+        <f t="shared" si="3"/>
+        <v>310</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M18" s="10" t="s">
         <v>54</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
-        <v>46260</v>
+        <v>46264</v>
       </c>
       <c r="B19" s="9">
-        <v>420</v>
+        <v>510</v>
       </c>
       <c r="C19" s="9">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="D19" s="9">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="E19" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F19" s="9">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G19" s="9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H19" s="9">
-        <v>180</v>
+        <v>310</v>
       </c>
       <c r="I19" s="14">
         <f t="shared" si="2"/>
-        <v>1040</v>
+        <v>1045</v>
       </c>
       <c r="J19" s="14">
         <f t="shared" si="3"/>
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="K19" s="10" t="s">
         <v>49</v>
@@ -1779,317 +1758,317 @@
         <v>51</v>
       </c>
       <c r="N19" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B20" s="9">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="C20" s="9">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D20" s="9">
-        <v>180</v>
+        <v>115</v>
       </c>
       <c r="E20" s="9">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="F20" s="9">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G20" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H20" s="9">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="I20" s="14">
         <f t="shared" si="2"/>
-        <v>1215</v>
+        <v>1090</v>
       </c>
       <c r="J20" s="14">
         <f t="shared" si="3"/>
-        <v>225</v>
+        <v>350</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N20" s="11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B21" s="9">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="C21" s="9">
         <v>30</v>
       </c>
       <c r="D21" s="9">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E21" s="9">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="F21" s="9">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="G21" s="9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H21" s="9">
-        <v>210</v>
+        <v>145</v>
       </c>
       <c r="I21" s="14">
         <f t="shared" si="2"/>
-        <v>1280</v>
+        <v>1140</v>
       </c>
       <c r="J21" s="14">
         <f t="shared" si="3"/>
-        <v>160</v>
+        <v>300</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="L21" s="10" t="s">
         <v>50</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="N21" s="11" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
-        <v>46263</v>
+        <v>46267</v>
       </c>
       <c r="B22" s="9">
-        <v>510</v>
+        <v>420</v>
       </c>
       <c r="C22" s="9">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D22" s="9">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="E22" s="9">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="F22" s="9">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G22" s="9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H22" s="9">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="I22" s="14">
         <f t="shared" si="2"/>
-        <v>1130</v>
+        <v>1075</v>
       </c>
       <c r="J22" s="14">
         <f t="shared" si="3"/>
-        <v>310</v>
+        <v>365</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M22" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="N22" s="11" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="N22" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
-        <v>46264</v>
+        <v>46268</v>
       </c>
       <c r="B23" s="9">
-        <v>510</v>
+        <v>450</v>
       </c>
       <c r="C23" s="9">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D23" s="9">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="E23" s="9">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="F23" s="9">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G23" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H23" s="9">
-        <v>270</v>
+        <v>160</v>
       </c>
       <c r="I23" s="14">
         <f t="shared" si="2"/>
-        <v>1125</v>
+        <v>1130</v>
       </c>
       <c r="J23" s="14">
         <f t="shared" si="3"/>
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="L23" s="10" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="M23" s="10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N23" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
-        <v>46265</v>
+        <v>46269</v>
       </c>
       <c r="B24" s="9">
         <v>420</v>
       </c>
       <c r="C24" s="9">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="D24" s="9">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="E24" s="9">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F24" s="9">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="G24" s="9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H24" s="9">
         <v>180</v>
       </c>
       <c r="I24" s="14">
         <f t="shared" si="2"/>
-        <v>1105</v>
+        <v>1120</v>
       </c>
       <c r="J24" s="14">
         <f t="shared" si="3"/>
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L24" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="M24" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="N24" s="11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="8">
+        <v>46270</v>
+      </c>
+      <c r="B25" s="9">
+        <v>510</v>
+      </c>
+      <c r="C25" s="9">
         <v>50</v>
       </c>
-      <c r="M24" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="N24" s="11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="8">
-        <v>46266</v>
-      </c>
-      <c r="B25" s="9">
-        <v>450</v>
-      </c>
-      <c r="C25" s="9">
-        <v>30</v>
-      </c>
       <c r="D25" s="9">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E25" s="9">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="F25" s="9">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G25" s="9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H25" s="9">
-        <v>150</v>
+        <v>205</v>
       </c>
       <c r="I25" s="14">
         <f t="shared" si="2"/>
-        <v>1150</v>
+        <v>1120</v>
       </c>
       <c r="J25" s="14">
         <f t="shared" si="3"/>
+        <v>320</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="L25" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="M25" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N25" s="11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="8">
+        <v>46271</v>
+      </c>
+      <c r="B26" s="9">
+        <v>480</v>
+      </c>
+      <c r="C26" s="9">
+        <v>40</v>
+      </c>
+      <c r="D26" s="9">
+        <v>130</v>
+      </c>
+      <c r="E26" s="9">
+        <v>75</v>
+      </c>
+      <c r="F26" s="9">
+        <v>0</v>
+      </c>
+      <c r="G26" s="9">
+        <v>0</v>
+      </c>
+      <c r="H26" s="9">
         <v>290</v>
-      </c>
-      <c r="K25" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="L25" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="M25" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="N25" s="11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="8">
-        <v>46267</v>
-      </c>
-      <c r="B26" s="9">
-        <v>420</v>
-      </c>
-      <c r="C26" s="9">
-        <v>45</v>
-      </c>
-      <c r="D26" s="9">
-        <v>120</v>
-      </c>
-      <c r="E26" s="9">
-        <v>90</v>
-      </c>
-      <c r="F26" s="9">
-        <v>200</v>
-      </c>
-      <c r="G26" s="9">
-        <v>4</v>
-      </c>
-      <c r="H26" s="9">
-        <v>180</v>
       </c>
       <c r="I26" s="14">
         <f t="shared" si="2"/>
-        <v>1055</v>
+        <v>1015</v>
       </c>
       <c r="J26" s="14">
         <f t="shared" si="3"/>
-        <v>385</v>
+        <v>425</v>
       </c>
       <c r="K26" s="10" t="s">
         <v>49</v>
@@ -2100,295 +2079,295 @@
       <c r="M26" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="N26" s="17" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="N26" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="B27" s="9">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="C27" s="9">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D27" s="9">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="E27" s="9">
         <v>90</v>
       </c>
       <c r="F27" s="9">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G27" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H27" s="9">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="I27" s="14">
         <f t="shared" si="2"/>
-        <v>1170</v>
+        <v>1090</v>
       </c>
       <c r="J27" s="14">
         <f t="shared" si="3"/>
-        <v>270</v>
+        <v>350</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L27" s="10" t="s">
         <v>50</v>
       </c>
       <c r="M27" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N27" s="11" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B28" s="9">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="C28" s="9">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D28" s="9">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="E28" s="9">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="F28" s="9">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="G28" s="9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H28" s="9">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="I28" s="14">
         <f t="shared" si="2"/>
-        <v>1190</v>
+        <v>1130</v>
       </c>
       <c r="J28" s="14">
         <f t="shared" si="3"/>
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="L28" s="10" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M28" s="10" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="N28" s="11" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
-        <v>46270</v>
+        <v>46274</v>
       </c>
       <c r="B29" s="9">
-        <v>510</v>
+        <v>420</v>
       </c>
       <c r="C29" s="9">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D29" s="9">
+        <v>110</v>
+      </c>
+      <c r="E29" s="9">
+        <v>120</v>
+      </c>
+      <c r="F29" s="9">
+        <v>200</v>
+      </c>
+      <c r="G29" s="9">
+        <v>4</v>
+      </c>
+      <c r="H29" s="9">
         <v>180</v>
-      </c>
-      <c r="E29" s="9">
-        <v>150</v>
-      </c>
-      <c r="F29" s="9">
-        <v>0</v>
-      </c>
-      <c r="G29" s="9">
-        <v>0</v>
-      </c>
-      <c r="H29" s="9">
-        <v>240</v>
       </c>
       <c r="I29" s="14">
         <f t="shared" si="2"/>
-        <v>1140</v>
+        <v>1080</v>
       </c>
       <c r="J29" s="14">
         <f t="shared" si="3"/>
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="L29" s="10" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="M29" s="10" t="s">
         <v>54</v>
       </c>
       <c r="N29" s="11" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
-        <v>46271</v>
+        <v>46275</v>
       </c>
       <c r="B30" s="9">
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="C30" s="9">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D30" s="9">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="E30" s="9">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="F30" s="9">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G30" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H30" s="9">
-        <v>300</v>
+        <v>155</v>
       </c>
       <c r="I30" s="14">
         <f t="shared" si="2"/>
-        <v>1095</v>
+        <v>1135</v>
       </c>
       <c r="J30" s="14">
         <f t="shared" si="3"/>
-        <v>345</v>
+        <v>305</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="L30" s="10" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M30" s="10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="N30" s="11" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
-        <v>46272</v>
+        <v>46276</v>
       </c>
       <c r="B31" s="9">
         <v>420</v>
       </c>
       <c r="C31" s="9">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D31" s="9">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="E31" s="9">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="F31" s="9">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="G31" s="9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H31" s="9">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="I31" s="14">
         <f t="shared" si="2"/>
-        <v>1105</v>
+        <v>1120</v>
       </c>
       <c r="J31" s="14">
         <f t="shared" si="3"/>
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L31" s="10" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M31" s="10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N31" s="11" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="8">
-        <v>46273</v>
+        <v>46277</v>
       </c>
       <c r="B32" s="9">
-        <v>450</v>
+        <v>510</v>
       </c>
       <c r="C32" s="9">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D32" s="9">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="E32" s="9">
-        <v>120</v>
+        <v>185</v>
       </c>
       <c r="F32" s="9">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G32" s="9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H32" s="9">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="I32" s="14">
         <f t="shared" si="2"/>
-        <v>1150</v>
+        <v>1135</v>
       </c>
       <c r="J32" s="14">
         <f t="shared" si="3"/>
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L32" s="10" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="M32" s="10" t="s">
         <v>54</v>
       </c>
       <c r="N32" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
-        <v>46274</v>
+        <v>46278</v>
       </c>
       <c r="B33" s="9">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="C33" s="9">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D33" s="9">
         <v>120</v>
@@ -2397,21 +2376,21 @@
         <v>90</v>
       </c>
       <c r="F33" s="9">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G33" s="9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H33" s="9">
-        <v>180</v>
+        <v>295</v>
       </c>
       <c r="I33" s="14">
         <f t="shared" si="2"/>
-        <v>1070</v>
+        <v>1030</v>
       </c>
       <c r="J33" s="14">
         <f t="shared" si="3"/>
-        <v>370</v>
+        <v>410</v>
       </c>
       <c r="K33" s="10" t="s">
         <v>49</v>
@@ -2420,99 +2399,99 @@
         <v>50</v>
       </c>
       <c r="M33" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N33" s="11" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B34" s="9">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="C34" s="9">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D34" s="9">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E34" s="9">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F34" s="9">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G34" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H34" s="9">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I34" s="14">
         <f t="shared" si="2"/>
-        <v>1170</v>
+        <v>1090</v>
       </c>
       <c r="J34" s="14">
         <f t="shared" si="3"/>
-        <v>270</v>
+        <v>350</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L34" s="10" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M34" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N34" s="11" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B35" s="9">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="C35" s="9">
         <v>30</v>
       </c>
       <c r="D35" s="9">
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="E35" s="9">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="F35" s="9">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="G35" s="9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H35" s="9">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="I35" s="14">
         <f t="shared" si="2"/>
-        <v>1190</v>
+        <v>1130</v>
       </c>
       <c r="J35" s="14">
         <f t="shared" si="3"/>
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="L35" s="10" t="s">
         <v>50</v>
       </c>
       <c r="M35" s="10" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="N35" s="11" t="s">
         <v>81</v>
@@ -2520,220 +2499,220 @@
     </row>
     <row r="36" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
-        <v>46277</v>
+        <v>46281</v>
       </c>
       <c r="B36" s="9">
-        <v>510</v>
+        <v>420</v>
       </c>
       <c r="C36" s="9">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D36" s="9">
+        <v>100</v>
+      </c>
+      <c r="E36" s="9">
+        <v>135</v>
+      </c>
+      <c r="F36" s="9">
+        <v>200</v>
+      </c>
+      <c r="G36" s="9">
+        <v>4</v>
+      </c>
+      <c r="H36" s="9">
         <v>180</v>
-      </c>
-      <c r="E36" s="9">
-        <v>150</v>
-      </c>
-      <c r="F36" s="9">
-        <v>0</v>
-      </c>
-      <c r="G36" s="9">
-        <v>0</v>
-      </c>
-      <c r="H36" s="9">
-        <v>240</v>
       </c>
       <c r="I36" s="14">
         <f t="shared" si="2"/>
-        <v>1140</v>
+        <v>1090</v>
       </c>
       <c r="J36" s="14">
         <f t="shared" si="3"/>
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="K36" s="10" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="L36" s="10" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="M36" s="10" t="s">
         <v>54</v>
       </c>
       <c r="N36" s="11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
-        <v>46278</v>
+        <v>46282</v>
       </c>
       <c r="B37" s="9">
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="C37" s="9">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D37" s="9">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="E37" s="9">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="F37" s="9">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G37" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H37" s="9">
-        <v>300</v>
+        <v>160</v>
       </c>
       <c r="I37" s="14">
         <f t="shared" si="2"/>
-        <v>1095</v>
+        <v>1135</v>
       </c>
       <c r="J37" s="14">
         <f t="shared" si="3"/>
-        <v>345</v>
+        <v>305</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="L37" s="10" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M37" s="10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="N37" s="11" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="B38" s="9">
         <v>420</v>
       </c>
       <c r="C38" s="9">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D38" s="9">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="E38" s="9">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F38" s="9">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="G38" s="9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H38" s="9">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="I38" s="14">
         <f t="shared" si="2"/>
-        <v>1105</v>
+        <v>1130</v>
       </c>
       <c r="J38" s="14">
         <f t="shared" si="3"/>
-        <v>335</v>
+        <v>310</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L38" s="10" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="M38" s="10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N38" s="11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
-        <v>46280</v>
+        <v>46284</v>
       </c>
       <c r="B39" s="9">
-        <v>450</v>
+        <v>510</v>
       </c>
       <c r="C39" s="9">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="D39" s="9">
         <v>150</v>
       </c>
       <c r="E39" s="9">
-        <v>120</v>
+        <v>195</v>
       </c>
       <c r="F39" s="9">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G39" s="9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H39" s="9">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="I39" s="14">
         <f t="shared" si="2"/>
-        <v>1150</v>
+        <v>1130</v>
       </c>
       <c r="J39" s="14">
         <f t="shared" si="3"/>
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="K39" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L39" s="10" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="M39" s="10" t="s">
         <v>54</v>
       </c>
       <c r="N39" s="11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40" s="8">
-        <v>46281</v>
+        <v>46285</v>
       </c>
       <c r="B40" s="9">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="C40" s="9">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="D40" s="9">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E40" s="9">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F40" s="9">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G40" s="9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H40" s="9">
-        <v>180</v>
+        <v>305</v>
       </c>
       <c r="I40" s="14">
         <f t="shared" si="2"/>
-        <v>1070</v>
+        <v>1020</v>
       </c>
       <c r="J40" s="14">
         <f t="shared" si="3"/>
-        <v>370</v>
+        <v>420</v>
       </c>
       <c r="K40" s="10" t="s">
         <v>49</v>
@@ -2745,238 +2724,118 @@
         <v>51</v>
       </c>
       <c r="N40" s="11" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A41" s="8">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="B41" s="9">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="C41" s="9">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D41" s="9">
         <v>120</v>
       </c>
       <c r="E41" s="9">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F41" s="9">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G41" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H41" s="9">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="I41" s="14">
         <f t="shared" si="2"/>
-        <v>1170</v>
+        <v>1095</v>
       </c>
       <c r="J41" s="14">
         <f t="shared" si="3"/>
-        <v>270</v>
+        <v>345</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L41" s="10" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M41" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N41" s="11" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="8">
-        <v>46283</v>
-      </c>
-      <c r="B42" s="9">
-        <v>420</v>
-      </c>
-      <c r="C42" s="9">
-        <v>30</v>
-      </c>
-      <c r="D42" s="9">
-        <v>90</v>
-      </c>
-      <c r="E42" s="9">
-        <v>120</v>
-      </c>
-      <c r="F42" s="9">
-        <v>350</v>
-      </c>
-      <c r="G42" s="9">
-        <v>7</v>
-      </c>
-      <c r="H42" s="9">
-        <v>180</v>
-      </c>
-      <c r="I42" s="14">
-        <f t="shared" si="2"/>
-        <v>1190</v>
-      </c>
-      <c r="J42" s="14">
-        <f t="shared" si="3"/>
-        <v>250</v>
-      </c>
-      <c r="K42" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="L42" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="M42" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="N42" s="11" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="8">
-        <v>46284</v>
-      </c>
-      <c r="B43" s="9">
-        <v>510</v>
-      </c>
-      <c r="C43" s="9">
-        <v>60</v>
-      </c>
-      <c r="D43" s="9">
-        <v>180</v>
-      </c>
-      <c r="E43" s="9">
-        <v>150</v>
-      </c>
-      <c r="F43" s="9">
-        <v>0</v>
-      </c>
-      <c r="G43" s="9">
-        <v>0</v>
-      </c>
-      <c r="H43" s="9">
-        <v>240</v>
-      </c>
-      <c r="I43" s="14">
-        <f t="shared" si="2"/>
-        <v>1140</v>
-      </c>
-      <c r="J43" s="14">
-        <f t="shared" si="3"/>
-        <v>300</v>
-      </c>
-      <c r="K43" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="L43" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="M43" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="N43" s="11" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A44" s="8">
-        <v>46285</v>
-      </c>
-      <c r="B44" s="9">
-        <v>480</v>
-      </c>
-      <c r="C44" s="9">
-        <v>45</v>
-      </c>
-      <c r="D44" s="9">
-        <v>150</v>
-      </c>
-      <c r="E44" s="9">
-        <v>120</v>
-      </c>
-      <c r="F44" s="9">
-        <v>0</v>
-      </c>
-      <c r="G44" s="9">
-        <v>0</v>
-      </c>
-      <c r="H44" s="9">
-        <v>300</v>
-      </c>
-      <c r="I44" s="14">
-        <f t="shared" si="2"/>
-        <v>1095</v>
-      </c>
-      <c r="J44" s="14">
-        <f t="shared" si="3"/>
-        <v>345</v>
-      </c>
-      <c r="K44" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="L44" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="M44" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="N44" s="11" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="8">
-        <v>46286</v>
-      </c>
-      <c r="B45" s="9">
-        <v>420</v>
-      </c>
-      <c r="C45" s="9">
-        <v>45</v>
-      </c>
-      <c r="D45" s="9">
-        <v>120</v>
-      </c>
-      <c r="E45" s="9">
-        <v>90</v>
-      </c>
-      <c r="F45" s="9">
-        <v>250</v>
-      </c>
-      <c r="G45" s="9">
-        <v>5</v>
-      </c>
-      <c r="H45" s="9">
-        <v>180</v>
-      </c>
-      <c r="I45" s="14">
-        <f t="shared" si="2"/>
-        <v>1105</v>
-      </c>
-      <c r="J45" s="14">
-        <f t="shared" si="3"/>
-        <v>335</v>
-      </c>
-      <c r="K45" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="L45" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="M45" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="N45" s="11" t="s">
-        <v>105</v>
-      </c>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42" s="8"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="14"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="10"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="11"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43" s="8"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="14"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="11"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A44" s="8"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="14"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="11"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A45" s="8"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="14"/>
+      <c r="J45" s="14"/>
+      <c r="K45" s="10"/>
+      <c r="L45" s="10"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="11"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="8"/>
@@ -2987,8 +2846,14 @@
       <c r="F46" s="9"/>
       <c r="G46" s="9"/>
       <c r="H46" s="9"/>
-      <c r="I46" s="14"/>
-      <c r="J46" s="14"/>
+      <c r="I46" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J46" s="14" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="K46" s="10"/>
       <c r="L46" s="10"/>
       <c r="M46" s="10"/>
@@ -3003,8 +2868,14 @@
       <c r="F47" s="9"/>
       <c r="G47" s="9"/>
       <c r="H47" s="9"/>
-      <c r="I47" s="14"/>
-      <c r="J47" s="14"/>
+      <c r="I47" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J47" s="14" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="K47" s="10"/>
       <c r="L47" s="10"/>
       <c r="M47" s="10"/>
@@ -3019,8 +2890,14 @@
       <c r="F48" s="9"/>
       <c r="G48" s="9"/>
       <c r="H48" s="9"/>
-      <c r="I48" s="14"/>
-      <c r="J48" s="14"/>
+      <c r="I48" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J48" s="14" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="K48" s="10"/>
       <c r="L48" s="10"/>
       <c r="M48" s="10"/>
@@ -3035,8 +2912,14 @@
       <c r="F49" s="9"/>
       <c r="G49" s="9"/>
       <c r="H49" s="9"/>
-      <c r="I49" s="14"/>
-      <c r="J49" s="14"/>
+      <c r="I49" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J49" s="14" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="K49" s="10"/>
       <c r="L49" s="10"/>
       <c r="M49" s="10"/>
@@ -3646,11 +3529,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I77:I140" si="4">IF(SUM(B77:F77,H77)=0,"",SUM(B77:F77,H77))</f>
         <v/>
       </c>
       <c r="J77" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J77:J140" si="5">IF(I77="","",1440-I77)</f>
         <v/>
       </c>
       <c r="K77" s="10"/>
@@ -3668,11 +3551,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J78" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K78" s="10"/>
@@ -3690,11 +3573,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J79" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K79" s="10"/>
@@ -3712,11 +3595,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J80" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K80" s="10"/>
@@ -3734,11 +3617,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="14" t="str">
-        <f t="shared" ref="I81:I144" si="4">IF(SUM(B81:F81,H81)=0,"",SUM(B81:F81,H81))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J81" s="14" t="str">
-        <f t="shared" ref="J81:J144" si="5">IF(I81="","",1440-I81)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K81" s="10"/>
@@ -5054,11 +4937,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I141:I204" si="6">IF(SUM(B141:F141,H141)=0,"",SUM(B141:F141,H141))</f>
         <v/>
       </c>
       <c r="J141" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J141:J204" si="7">IF(I141="","",1440-I141)</f>
         <v/>
       </c>
       <c r="K141" s="10"/>
@@ -5076,11 +4959,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J142" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K142" s="10"/>
@@ -5090,19 +4973,19 @@
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A143" s="8"/>
-      <c r="B143" s="9"/>
-      <c r="C143" s="9"/>
-      <c r="D143" s="9"/>
-      <c r="E143" s="9"/>
-      <c r="F143" s="9"/>
-      <c r="G143" s="9"/>
+      <c r="B143" s="13"/>
+      <c r="C143" s="13"/>
+      <c r="D143" s="13"/>
+      <c r="E143" s="13"/>
+      <c r="F143" s="13"/>
+      <c r="G143" s="13"/>
       <c r="H143" s="9"/>
       <c r="I143" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J143" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K143" s="10"/>
@@ -5112,57 +4995,57 @@
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A144" s="8"/>
-      <c r="B144" s="9"/>
-      <c r="C144" s="9"/>
-      <c r="D144" s="9"/>
-      <c r="E144" s="9"/>
-      <c r="F144" s="9"/>
-      <c r="G144" s="9"/>
-      <c r="H144" s="9"/>
+      <c r="B144" s="13"/>
+      <c r="C144" s="13"/>
+      <c r="D144" s="13"/>
+      <c r="E144" s="13"/>
+      <c r="F144" s="13"/>
+      <c r="G144" s="13"/>
+      <c r="H144" s="13"/>
       <c r="I144" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J144" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K144" s="10"/>
-      <c r="L144" s="10"/>
-      <c r="M144" s="10"/>
-      <c r="N144" s="11"/>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="K144" s="15"/>
+      <c r="L144" s="15"/>
+      <c r="M144" s="15"/>
+      <c r="N144" s="16"/>
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A145" s="8"/>
-      <c r="B145" s="9"/>
-      <c r="C145" s="9"/>
-      <c r="D145" s="9"/>
-      <c r="E145" s="9"/>
-      <c r="F145" s="9"/>
-      <c r="G145" s="9"/>
-      <c r="H145" s="9"/>
+      <c r="B145" s="13"/>
+      <c r="C145" s="13"/>
+      <c r="D145" s="13"/>
+      <c r="E145" s="13"/>
+      <c r="F145" s="13"/>
+      <c r="G145" s="13"/>
+      <c r="H145" s="13"/>
       <c r="I145" s="14" t="str">
-        <f t="shared" ref="I145:I208" si="6">IF(SUM(B145:F145,H145)=0,"",SUM(B145:F145,H145))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J145" s="14" t="str">
-        <f t="shared" ref="J145:J208" si="7">IF(I145="","",1440-I145)</f>
-        <v/>
-      </c>
-      <c r="K145" s="10"/>
-      <c r="L145" s="10"/>
-      <c r="M145" s="10"/>
-      <c r="N145" s="11"/>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="K145" s="15"/>
+      <c r="L145" s="15"/>
+      <c r="M145" s="15"/>
+      <c r="N145" s="16"/>
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A146" s="8"/>
-      <c r="B146" s="9"/>
-      <c r="C146" s="9"/>
-      <c r="D146" s="9"/>
-      <c r="E146" s="9"/>
-      <c r="F146" s="9"/>
-      <c r="G146" s="9"/>
-      <c r="H146" s="9"/>
+      <c r="B146" s="13"/>
+      <c r="C146" s="13"/>
+      <c r="D146" s="13"/>
+      <c r="E146" s="13"/>
+      <c r="F146" s="13"/>
+      <c r="G146" s="13"/>
+      <c r="H146" s="13"/>
       <c r="I146" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -5171,10 +5054,10 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K146" s="10"/>
-      <c r="L146" s="10"/>
-      <c r="M146" s="10"/>
-      <c r="N146" s="11"/>
+      <c r="K146" s="15"/>
+      <c r="L146" s="15"/>
+      <c r="M146" s="15"/>
+      <c r="N146" s="16"/>
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A147" s="8"/>
@@ -5184,7 +5067,7 @@
       <c r="E147" s="13"/>
       <c r="F147" s="13"/>
       <c r="G147" s="13"/>
-      <c r="H147" s="9"/>
+      <c r="H147" s="13"/>
       <c r="I147" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -5193,10 +5076,10 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K147" s="10"/>
-      <c r="L147" s="10"/>
-      <c r="M147" s="10"/>
-      <c r="N147" s="11"/>
+      <c r="K147" s="15"/>
+      <c r="L147" s="15"/>
+      <c r="M147" s="15"/>
+      <c r="N147" s="16"/>
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A148" s="8"/>
@@ -6462,11 +6345,11 @@
       <c r="G205" s="13"/>
       <c r="H205" s="13"/>
       <c r="I205" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I205:I268" si="8">IF(SUM(B205:F205,H205)=0,"",SUM(B205:F205,H205))</f>
         <v/>
       </c>
       <c r="J205" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J205:J268" si="9">IF(I205="","",1440-I205)</f>
         <v/>
       </c>
       <c r="K205" s="15"/>
@@ -6484,11 +6367,11 @@
       <c r="G206" s="13"/>
       <c r="H206" s="13"/>
       <c r="I206" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J206" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K206" s="15"/>
@@ -6506,11 +6389,11 @@
       <c r="G207" s="13"/>
       <c r="H207" s="13"/>
       <c r="I207" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J207" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K207" s="15"/>
@@ -6528,11 +6411,11 @@
       <c r="G208" s="13"/>
       <c r="H208" s="13"/>
       <c r="I208" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J208" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K208" s="15"/>
@@ -6550,11 +6433,11 @@
       <c r="G209" s="13"/>
       <c r="H209" s="13"/>
       <c r="I209" s="14" t="str">
-        <f t="shared" ref="I209:I272" si="8">IF(SUM(B209:F209,H209)=0,"",SUM(B209:F209,H209))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J209" s="14" t="str">
-        <f t="shared" ref="J209:J272" si="9">IF(I209="","",1440-I209)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K209" s="15"/>
@@ -6761,7 +6644,7 @@
       <c r="N218" s="16"/>
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A219" s="8"/>
+      <c r="A219" s="12"/>
       <c r="B219" s="13"/>
       <c r="C219" s="13"/>
       <c r="D219" s="13"/>
@@ -6783,7 +6666,7 @@
       <c r="N219" s="16"/>
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A220" s="8"/>
+      <c r="A220" s="12"/>
       <c r="B220" s="13"/>
       <c r="C220" s="13"/>
       <c r="D220" s="13"/>
@@ -6805,7 +6688,7 @@
       <c r="N220" s="16"/>
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A221" s="8"/>
+      <c r="A221" s="12"/>
       <c r="B221" s="13"/>
       <c r="C221" s="13"/>
       <c r="D221" s="13"/>
@@ -6827,7 +6710,7 @@
       <c r="N221" s="16"/>
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A222" s="8"/>
+      <c r="A222" s="12"/>
       <c r="B222" s="13"/>
       <c r="C222" s="13"/>
       <c r="D222" s="13"/>
@@ -7870,11 +7753,11 @@
       <c r="G269" s="13"/>
       <c r="H269" s="13"/>
       <c r="I269" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I269:I332" si="10">IF(SUM(B269:F269,H269)=0,"",SUM(B269:F269,H269))</f>
         <v/>
       </c>
       <c r="J269" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J269:J332" si="11">IF(I269="","",1440-I269)</f>
         <v/>
       </c>
       <c r="K269" s="15"/>
@@ -7892,11 +7775,11 @@
       <c r="G270" s="13"/>
       <c r="H270" s="13"/>
       <c r="I270" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J270" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K270" s="15"/>
@@ -7914,11 +7797,11 @@
       <c r="G271" s="13"/>
       <c r="H271" s="13"/>
       <c r="I271" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J271" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K271" s="15"/>
@@ -7936,11 +7819,11 @@
       <c r="G272" s="13"/>
       <c r="H272" s="13"/>
       <c r="I272" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J272" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K272" s="15"/>
@@ -7958,11 +7841,11 @@
       <c r="G273" s="13"/>
       <c r="H273" s="13"/>
       <c r="I273" s="14" t="str">
-        <f t="shared" ref="I273:I336" si="10">IF(SUM(B273:F273,H273)=0,"",SUM(B273:F273,H273))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J273" s="14" t="str">
-        <f t="shared" ref="J273:J336" si="11">IF(I273="","",1440-I273)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K273" s="15"/>
@@ -9278,11 +9161,11 @@
       <c r="G333" s="13"/>
       <c r="H333" s="13"/>
       <c r="I333" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I333:I396" si="12">IF(SUM(B333:F333,H333)=0,"",SUM(B333:F333,H333))</f>
         <v/>
       </c>
       <c r="J333" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J333:J396" si="13">IF(I333="","",1440-I333)</f>
         <v/>
       </c>
       <c r="K333" s="15"/>
@@ -9300,11 +9183,11 @@
       <c r="G334" s="13"/>
       <c r="H334" s="13"/>
       <c r="I334" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J334" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K334" s="15"/>
@@ -9322,11 +9205,11 @@
       <c r="G335" s="13"/>
       <c r="H335" s="13"/>
       <c r="I335" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J335" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K335" s="15"/>
@@ -9344,11 +9227,11 @@
       <c r="G336" s="13"/>
       <c r="H336" s="13"/>
       <c r="I336" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J336" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K336" s="15"/>
@@ -9366,11 +9249,11 @@
       <c r="G337" s="13"/>
       <c r="H337" s="13"/>
       <c r="I337" s="14" t="str">
-        <f t="shared" ref="I337:I400" si="12">IF(SUM(B337:F337,H337)=0,"",SUM(B337:F337,H337))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J337" s="14" t="str">
-        <f t="shared" ref="J337:J400" si="13">IF(I337="","",1440-I337)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K337" s="15"/>
@@ -10686,11 +10569,11 @@
       <c r="G397" s="13"/>
       <c r="H397" s="13"/>
       <c r="I397" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="I397:I408" si="14">IF(SUM(B397:F397,H397)=0,"",SUM(B397:F397,H397))</f>
         <v/>
       </c>
       <c r="J397" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="J397:J408" si="15">IF(I397="","",1440-I397)</f>
         <v/>
       </c>
       <c r="K397" s="15"/>
@@ -10708,11 +10591,11 @@
       <c r="G398" s="13"/>
       <c r="H398" s="13"/>
       <c r="I398" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J398" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K398" s="15"/>
@@ -10730,11 +10613,11 @@
       <c r="G399" s="13"/>
       <c r="H399" s="13"/>
       <c r="I399" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J399" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K399" s="15"/>
@@ -10752,11 +10635,11 @@
       <c r="G400" s="13"/>
       <c r="H400" s="13"/>
       <c r="I400" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J400" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K400" s="15"/>
@@ -10774,11 +10657,11 @@
       <c r="G401" s="13"/>
       <c r="H401" s="13"/>
       <c r="I401" s="14" t="str">
-        <f t="shared" ref="I401:I412" si="14">IF(SUM(B401:F401,H401)=0,"",SUM(B401:F401,H401))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J401" s="14" t="str">
-        <f t="shared" ref="J401:J412" si="15">IF(I401="","",1440-I401)</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K401" s="15"/>
@@ -10940,94 +10823,6 @@
       <c r="M408" s="15"/>
       <c r="N408" s="16"/>
     </row>
-    <row r="409" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A409" s="12"/>
-      <c r="B409" s="13"/>
-      <c r="C409" s="13"/>
-      <c r="D409" s="13"/>
-      <c r="E409" s="13"/>
-      <c r="F409" s="13"/>
-      <c r="G409" s="13"/>
-      <c r="H409" s="13"/>
-      <c r="I409" s="14" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J409" s="14" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K409" s="15"/>
-      <c r="L409" s="15"/>
-      <c r="M409" s="15"/>
-      <c r="N409" s="16"/>
-    </row>
-    <row r="410" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A410" s="12"/>
-      <c r="B410" s="13"/>
-      <c r="C410" s="13"/>
-      <c r="D410" s="13"/>
-      <c r="E410" s="13"/>
-      <c r="F410" s="13"/>
-      <c r="G410" s="13"/>
-      <c r="H410" s="13"/>
-      <c r="I410" s="14" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J410" s="14" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K410" s="15"/>
-      <c r="L410" s="15"/>
-      <c r="M410" s="15"/>
-      <c r="N410" s="16"/>
-    </row>
-    <row r="411" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A411" s="12"/>
-      <c r="B411" s="13"/>
-      <c r="C411" s="13"/>
-      <c r="D411" s="13"/>
-      <c r="E411" s="13"/>
-      <c r="F411" s="13"/>
-      <c r="G411" s="13"/>
-      <c r="H411" s="13"/>
-      <c r="I411" s="14" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J411" s="14" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K411" s="15"/>
-      <c r="L411" s="15"/>
-      <c r="M411" s="15"/>
-      <c r="N411" s="16"/>
-    </row>
-    <row r="412" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A412" s="12"/>
-      <c r="B412" s="13"/>
-      <c r="C412" s="13"/>
-      <c r="D412" s="13"/>
-      <c r="E412" s="13"/>
-      <c r="F412" s="13"/>
-      <c r="G412" s="13"/>
-      <c r="H412" s="13"/>
-      <c r="I412" s="14" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J412" s="14" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K412" s="15"/>
-      <c r="L412" s="15"/>
-      <c r="M412" s="15"/>
-      <c r="N412" s="16"/>
-    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:N4"/>
@@ -11037,21 +10832,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J412">
+  <conditionalFormatting sqref="J6:J408">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K412" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K408" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L412" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L408" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M412" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M408" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12600717.xlsx
+++ b/12600717.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python Minor Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24884B55-9BC4-4D2C-AB15-7F2623D5A770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1452010-0B0C-40FA-9E7D-F580DFF9824D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
